--- a/JsonConverter/ExcelFiles/Episode.xlsx
+++ b/JsonConverter/ExcelFiles/Episode.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="15900" windowHeight="6312"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="17868" windowHeight="6312"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="HeroBasic" sheetId="1" r:id="rId4"/>
@@ -19,15 +19,90 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+  <x:si>
+    <x:t>4일차에 발생하는 테스트 에피소드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5일차에 발생하는 테스트 에피소드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsArchiveVisible</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archive</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에피소드 분류</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PlaybackType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsRepeatable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxTriggerCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>episode_test_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>재생 방식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에피소드 내용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에피소드ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에피소드 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DialogueId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EpisodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>테스트 에피소드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연결 다이얼로그 ID</x:t>
+  </x:si>
   <x:si>
     <x:t>반복 발생 여부</x:t>
   </x:si>
   <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
+    <x:t>최대 발생 횟수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>episode_test_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Auto</x:t>
   </x:si>
   <x:si>
     <x:t>EpisodeDescription</x:t>
@@ -36,46 +111,22 @@
     <x:t>3일차에 발생하는 테스트 에피소드</x:t>
   </x:si>
   <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연결 다이얼로그 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsRepeatable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>episode_test_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxTriggerCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EpisodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>테스트 에피소드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DialogueId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에피소드 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에피소드ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최대 발생 횟수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에피소드 내용</x:t>
+    <x:t>도감 노출 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Main</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Daily</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Category</x:t>
+  </x:si>
+  <x:si>
+    <x:t>episode_test_02</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -127,12 +178,12 @@
       <x:name val="맑은 고딕"/>
       <x:sz val="11"/>
       <x:color rgb="ff000000"/>
-      <x:b val="1"/>
     </x:font>
     <x:font>
       <x:name val="맑은 고딕"/>
       <x:sz val="11"/>
       <x:color rgb="ff000000"/>
+      <x:b val="1"/>
     </x:font>
   </x:fonts>
   <x:fills count="7">
@@ -157,13 +208,13 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="ffffffff"/>
-        <x:bgColor rgb="ffffc000"/>
+        <x:bgColor rgb="ffd86dcd"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="ffffffff"/>
-        <x:bgColor rgb="ffd86dcd"/>
+        <x:bgColor rgb="ffffc000"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -230,16 +281,13 @@
     <x:xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -251,44 +299,47 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" hs:applyExtension="1">
+        <x:xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
           <x:alignment horizontal="center" vertical="center" wrapText="1"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
         </x:xf>
       </mc:Choice>
       <mc:Fallback>
-        <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+        <x:xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
           <x:alignment horizontal="center" vertical="center" wrapText="1"/>
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" hs:applyExtension="1">
+        <x:xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
           <x:alignment horizontal="right" vertical="center" wrapText="1"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
         </x:xf>
       </mc:Choice>
       <mc:Fallback>
-        <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+        <x:xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
           <x:alignment horizontal="right" vertical="center" wrapText="1"/>
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyAlignment="1" hs:applyExtension="1">
+        <x:xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
           <x:alignment horizontal="right" vertical="center" wrapText="1"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
         </x:xf>
       </mc:Choice>
       <mc:Fallback>
-        <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+        <x:xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
           <x:alignment horizontal="right" vertical="center" wrapText="1"/>
         </x:xf>
       </mc:Fallback>
@@ -897,196 +948,286 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:M35"/>
+  <x:dimension ref="A1:P35"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="19.42578125" style="3" customWidth="1"/>
     <x:col min="2" max="2" width="19.5703125" style="3" customWidth="1"/>
     <x:col min="3" max="3" width="32.76171875" style="3" bestFit="1" customWidth="1"/>
-    <x:col min="4" max="4" width="20.28515625" style="3" customWidth="1"/>
-    <x:col min="5" max="5" width="30.5703125" style="3" customWidth="1"/>
-    <x:col min="6" max="6" width="26.5703125" style="3" customWidth="1"/>
-    <x:col min="7" max="16384" width="12.5703125" style="3"/>
+    <x:col min="4" max="7" width="20.28515625" style="3" customWidth="1"/>
+    <x:col min="8" max="8" width="30.5703125" style="3" customWidth="1"/>
+    <x:col min="9" max="9" width="26.5703125" style="3" customWidth="1"/>
+    <x:col min="10" max="16384" width="12.5703125" style="3"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:6" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B1" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="C1" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D1" s="13" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E1" s="13" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F1" s="13" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G1" s="13" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H1" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I1" s="3" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:9" ht="13.199999999999999">
+      <x:c r="A2" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I2" s="1" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:9" s="11" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="14" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B3" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="D1" s="16" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="s">
+      <x:c r="C3" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E3" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F3" s="14" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G3" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H3" s="14" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I3" s="15" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A4" s="16" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C4" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D4" s="16" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E4" s="16" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F4" s="16" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G4" s="16" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H4" s="16" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F1" s="3" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:6" ht="13.199999999999999">
-      <x:c r="A2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
+      <x:c r="I4" s="17">
         <x:v>1</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:6" s="12" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B3" s="14" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C3" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E3" s="14" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F3" s="15" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A4" s="16" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B4" s="16" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C4" s="16" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E4" s="16" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F4" s="17">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G4" s="5"/>
-      <x:c r="H4" s="5"/>
-      <x:c r="I4" s="5"/>
       <x:c r="J4" s="5"/>
       <x:c r="K4" s="5"/>
       <x:c r="L4" s="5"/>
       <x:c r="M4" s="5"/>
-    </x:row>
-    <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A5" s="4"/>
-      <x:c r="B5" s="6"/>
-      <x:c r="C5" s="6"/>
-      <x:c r="D5" s="13"/>
-      <x:c r="E5" s="13"/>
-      <x:c r="F5" s="13"/>
-      <x:c r="G5" s="5"/>
-      <x:c r="H5" s="5"/>
-      <x:c r="I5" s="5"/>
+      <x:c r="N4" s="5"/>
+      <x:c r="O4" s="5"/>
+      <x:c r="P4" s="5"/>
+    </x:row>
+    <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A5" s="16" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B5" s="16" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C5" s="16" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D5" s="16" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E5" s="16" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F5" s="16" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G5" s="16" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H5" s="16" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I5" s="17">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="J5" s="5"/>
       <x:c r="K5" s="5"/>
       <x:c r="L5" s="5"/>
       <x:c r="M5" s="5"/>
-    </x:row>
-    <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A6" s="4"/>
-      <x:c r="B6" s="6"/>
-      <x:c r="C6" s="6"/>
-      <x:c r="D6" s="13"/>
-      <x:c r="E6" s="13"/>
-      <x:c r="F6" s="13"/>
-      <x:c r="G6" s="5"/>
-      <x:c r="H6" s="5"/>
-      <x:c r="I6" s="5"/>
+      <x:c r="N5" s="5"/>
+      <x:c r="O5" s="5"/>
+      <x:c r="P5" s="5"/>
+    </x:row>
+    <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A6" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B6" s="16" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C6" s="16" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D6" s="16" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E6" s="16" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F6" s="16" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G6" s="16" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H6" s="16" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I6" s="17">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="J6" s="5"/>
       <x:c r="K6" s="5"/>
       <x:c r="L6" s="5"/>
       <x:c r="M6" s="5"/>
-    </x:row>
-    <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="N6" s="5"/>
+      <x:c r="O6" s="5"/>
+      <x:c r="P6" s="5"/>
+    </x:row>
+    <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A7" s="4"/>
       <x:c r="B7" s="4"/>
       <x:c r="C7" s="4"/>
-      <x:c r="D7" s="13"/>
-      <x:c r="E7" s="13"/>
-      <x:c r="F7" s="13"/>
-      <x:c r="G7" s="5"/>
-      <x:c r="H7" s="5"/>
-      <x:c r="I7" s="5"/>
+      <x:c r="D7" s="12"/>
+      <x:c r="E7" s="12"/>
+      <x:c r="F7" s="12"/>
+      <x:c r="G7" s="12"/>
+      <x:c r="H7" s="12"/>
+      <x:c r="I7" s="12"/>
       <x:c r="J7" s="5"/>
       <x:c r="K7" s="5"/>
       <x:c r="L7" s="5"/>
       <x:c r="M7" s="5"/>
-    </x:row>
-    <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="N7" s="5"/>
+      <x:c r="O7" s="5"/>
+      <x:c r="P7" s="5"/>
+    </x:row>
+    <x:row r="8" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A8" s="4"/>
-      <x:c r="B8" s="7"/>
-      <x:c r="C8" s="7"/>
-      <x:c r="D8" s="13"/>
-      <x:c r="E8" s="13"/>
-      <x:c r="F8" s="13"/>
-      <x:c r="G8" s="5"/>
-      <x:c r="H8" s="5"/>
-      <x:c r="I8" s="5"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="12"/>
+      <x:c r="E8" s="12"/>
+      <x:c r="F8" s="12"/>
+      <x:c r="G8" s="12"/>
+      <x:c r="H8" s="12"/>
+      <x:c r="I8" s="12"/>
       <x:c r="J8" s="5"/>
       <x:c r="K8" s="5"/>
       <x:c r="L8" s="5"/>
       <x:c r="M8" s="5"/>
-    </x:row>
-    <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="N8" s="5"/>
+      <x:c r="O8" s="5"/>
+      <x:c r="P8" s="5"/>
+    </x:row>
+    <x:row r="9" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A9" s="4"/>
-      <x:c r="B9" s="7"/>
-      <x:c r="C9" s="7"/>
-      <x:c r="D9" s="13"/>
-      <x:c r="E9" s="13"/>
-      <x:c r="F9" s="13"/>
-      <x:c r="G9" s="5"/>
-      <x:c r="H9" s="5"/>
-      <x:c r="I9" s="5"/>
+      <x:c r="B9" s="6"/>
+      <x:c r="C9" s="6"/>
+      <x:c r="D9" s="12"/>
+      <x:c r="E9" s="12"/>
+      <x:c r="F9" s="12"/>
+      <x:c r="G9" s="12"/>
+      <x:c r="H9" s="12"/>
+      <x:c r="I9" s="12"/>
       <x:c r="J9" s="5"/>
       <x:c r="K9" s="5"/>
       <x:c r="L9" s="5"/>
       <x:c r="M9" s="5"/>
-    </x:row>
-    <x:row r="10" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="N9" s="5"/>
+      <x:c r="O9" s="5"/>
+      <x:c r="P9" s="5"/>
+    </x:row>
+    <x:row r="10" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A10" s="4"/>
       <x:c r="B10" s="1"/>
       <x:c r="C10" s="1"/>
-      <x:c r="D10" s="13"/>
-      <x:c r="E10" s="13"/>
-      <x:c r="F10" s="13"/>
-      <x:c r="G10" s="5"/>
-      <x:c r="H10" s="5"/>
-      <x:c r="I10" s="5"/>
+      <x:c r="D10" s="12"/>
+      <x:c r="E10" s="12"/>
+      <x:c r="F10" s="12"/>
+      <x:c r="G10" s="12"/>
+      <x:c r="H10" s="12"/>
+      <x:c r="I10" s="12"/>
       <x:c r="J10" s="5"/>
       <x:c r="K10" s="5"/>
       <x:c r="L10" s="5"/>
       <x:c r="M10" s="5"/>
-    </x:row>
-    <x:row r="11" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="N10" s="5"/>
+      <x:c r="O10" s="5"/>
+      <x:c r="P10" s="5"/>
+    </x:row>
+    <x:row r="11" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A11" s="1"/>
       <x:c r="B11" s="1"/>
       <x:c r="C11" s="1"/>
@@ -1100,11 +1241,14 @@
       <x:c r="K11" s="5"/>
       <x:c r="L11" s="5"/>
       <x:c r="M11" s="5"/>
-    </x:row>
-    <x:row r="12" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A12" s="7"/>
-      <x:c r="B12" s="7"/>
-      <x:c r="C12" s="7"/>
+      <x:c r="N11" s="5"/>
+      <x:c r="O11" s="5"/>
+      <x:c r="P11" s="5"/>
+    </x:row>
+    <x:row r="12" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A12" s="6"/>
+      <x:c r="B12" s="6"/>
+      <x:c r="C12" s="6"/>
       <x:c r="D12" s="5"/>
       <x:c r="E12" s="5"/>
       <x:c r="F12" s="5"/>
@@ -1115,8 +1259,11 @@
       <x:c r="K12" s="5"/>
       <x:c r="L12" s="5"/>
       <x:c r="M12" s="5"/>
-    </x:row>
-    <x:row r="13" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="N12" s="5"/>
+      <x:c r="O12" s="5"/>
+      <x:c r="P12" s="5"/>
+    </x:row>
+    <x:row r="13" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A13" s="4"/>
       <x:c r="B13" s="4"/>
       <x:c r="C13" s="4"/>
@@ -1130,8 +1277,11 @@
       <x:c r="K13" s="5"/>
       <x:c r="L13" s="5"/>
       <x:c r="M13" s="5"/>
-    </x:row>
-    <x:row r="14" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="N13" s="5"/>
+      <x:c r="O13" s="5"/>
+      <x:c r="P13" s="5"/>
+    </x:row>
+    <x:row r="14" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A14" s="1"/>
       <x:c r="B14" s="1"/>
       <x:c r="C14" s="1"/>
@@ -1145,8 +1295,11 @@
       <x:c r="K14" s="5"/>
       <x:c r="L14" s="5"/>
       <x:c r="M14" s="5"/>
-    </x:row>
-    <x:row r="15" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="N14" s="5"/>
+      <x:c r="O14" s="5"/>
+      <x:c r="P14" s="5"/>
+    </x:row>
+    <x:row r="15" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A15" s="1"/>
       <x:c r="B15" s="1"/>
       <x:c r="C15" s="1"/>
@@ -1160,112 +1313,118 @@
       <x:c r="K15" s="5"/>
       <x:c r="L15" s="5"/>
       <x:c r="M15" s="5"/>
+      <x:c r="N15" s="5"/>
+      <x:c r="O15" s="5"/>
+      <x:c r="P15" s="5"/>
     </x:row>
     <x:row r="16" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A16" s="8"/>
-      <x:c r="B16" s="8"/>
-      <x:c r="C16" s="8"/>
+      <x:c r="A16" s="7"/>
+      <x:c r="B16" s="7"/>
+      <x:c r="C16" s="7"/>
     </x:row>
     <x:row r="17" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A17" s="9"/>
-      <x:c r="B17" s="9"/>
-      <x:c r="C17" s="9"/>
+      <x:c r="A17" s="8"/>
+      <x:c r="B17" s="8"/>
+      <x:c r="C17" s="8"/>
     </x:row>
     <x:row r="18" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A18" s="9"/>
-      <x:c r="B18" s="9"/>
-      <x:c r="C18" s="9"/>
-    </x:row>
-    <x:row r="19" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A19" s="9"/>
-      <x:c r="B19" s="9"/>
-      <x:c r="C19" s="9"/>
+      <x:c r="A18" s="8"/>
+      <x:c r="B18" s="8"/>
+      <x:c r="C18" s="8"/>
+    </x:row>
+    <x:row r="19" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A19" s="8"/>
+      <x:c r="B19" s="8"/>
+      <x:c r="C19" s="8"/>
       <x:c r="D19" s="5"/>
       <x:c r="E19" s="5"/>
+      <x:c r="F19" s="5"/>
+      <x:c r="G19" s="5"/>
+      <x:c r="H19" s="5"/>
     </x:row>
     <x:row r="20" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A20" s="9"/>
-      <x:c r="B20" s="9"/>
-      <x:c r="C20" s="9"/>
+      <x:c r="A20" s="8"/>
+      <x:c r="B20" s="8"/>
+      <x:c r="C20" s="8"/>
     </x:row>
     <x:row r="21" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A21" s="9"/>
-      <x:c r="B21" s="9"/>
-      <x:c r="C21" s="9"/>
+      <x:c r="A21" s="8"/>
+      <x:c r="B21" s="8"/>
+      <x:c r="C21" s="8"/>
     </x:row>
     <x:row r="22" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A22" s="9"/>
-      <x:c r="B22" s="9"/>
-      <x:c r="C22" s="9"/>
+      <x:c r="A22" s="8"/>
+      <x:c r="B22" s="8"/>
+      <x:c r="C22" s="8"/>
     </x:row>
     <x:row r="23" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A23" s="9"/>
-      <x:c r="B23" s="9"/>
-      <x:c r="C23" s="9"/>
+      <x:c r="A23" s="8"/>
+      <x:c r="B23" s="8"/>
+      <x:c r="C23" s="8"/>
     </x:row>
     <x:row r="24" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A24" s="9"/>
-      <x:c r="B24" s="9"/>
-      <x:c r="C24" s="9"/>
-    </x:row>
-    <x:row r="25" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A25" s="9"/>
-      <x:c r="B25" s="9"/>
-      <x:c r="C25" s="9"/>
-      <x:c r="E25" s="5"/>
-    </x:row>
-    <x:row r="26" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A26" s="10"/>
-      <x:c r="B26" s="10"/>
-      <x:c r="C26" s="10"/>
-      <x:c r="E26" s="5"/>
-    </x:row>
-    <x:row r="27" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A27" s="10"/>
-      <x:c r="B27" s="10"/>
-      <x:c r="C27" s="10"/>
-      <x:c r="E27" s="5"/>
-    </x:row>
-    <x:row r="28" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A28" s="10"/>
-      <x:c r="B28" s="10"/>
-      <x:c r="C28" s="10"/>
-      <x:c r="E28" s="5"/>
+      <x:c r="A24" s="8"/>
+      <x:c r="B24" s="8"/>
+      <x:c r="C24" s="8"/>
+    </x:row>
+    <x:row r="25" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A25" s="8"/>
+      <x:c r="B25" s="8"/>
+      <x:c r="C25" s="8"/>
+      <x:c r="H25" s="5"/>
+    </x:row>
+    <x:row r="26" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A26" s="9"/>
+      <x:c r="B26" s="9"/>
+      <x:c r="C26" s="9"/>
+      <x:c r="H26" s="5"/>
+    </x:row>
+    <x:row r="27" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A27" s="9"/>
+      <x:c r="B27" s="9"/>
+      <x:c r="C27" s="9"/>
+      <x:c r="H27" s="5"/>
+    </x:row>
+    <x:row r="28" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A28" s="9"/>
+      <x:c r="B28" s="9"/>
+      <x:c r="C28" s="9"/>
+      <x:c r="H28" s="5"/>
     </x:row>
     <x:row r="29" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A29" s="10"/>
-      <x:c r="B29" s="10"/>
-      <x:c r="C29" s="10"/>
+      <x:c r="A29" s="9"/>
+      <x:c r="B29" s="9"/>
+      <x:c r="C29" s="9"/>
     </x:row>
     <x:row r="30" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A30" s="10"/>
-      <x:c r="B30" s="10"/>
-      <x:c r="C30" s="10"/>
+      <x:c r="A30" s="9"/>
+      <x:c r="B30" s="9"/>
+      <x:c r="C30" s="9"/>
     </x:row>
     <x:row r="31" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A31" s="10"/>
-      <x:c r="B31" s="10"/>
-      <x:c r="C31" s="10"/>
+      <x:c r="A31" s="9"/>
+      <x:c r="B31" s="9"/>
+      <x:c r="C31" s="9"/>
     </x:row>
     <x:row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A32" s="11"/>
-      <x:c r="B32" s="11"/>
-      <x:c r="C32" s="11"/>
+      <x:c r="A32" s="10"/>
+      <x:c r="B32" s="10"/>
+      <x:c r="C32" s="10"/>
     </x:row>
     <x:row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A33" s="11"/>
-      <x:c r="B33" s="11"/>
-      <x:c r="C33" s="11"/>
+      <x:c r="A33" s="10"/>
+      <x:c r="B33" s="10"/>
+      <x:c r="C33" s="10"/>
     </x:row>
     <x:row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A34" s="11"/>
-      <x:c r="B34" s="11"/>
-      <x:c r="C34" s="11"/>
+      <x:c r="A34" s="10"/>
+      <x:c r="B34" s="10"/>
+      <x:c r="C34" s="10"/>
     </x:row>
     <x:row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A35" s="11"/>
-      <x:c r="B35" s="11"/>
-      <x:c r="C35" s="11"/>
+      <x:c r="A35" s="10"/>
+      <x:c r="B35" s="10"/>
+      <x:c r="C35" s="10"/>
     </x:row>
     <x:row r="36" ht="15.75" customHeight="1"/>
     <x:row r="37" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Episode.xlsx
+++ b/JsonConverter/ExcelFiles/Episode.xlsx
@@ -19,114 +19,105 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
+  <x:si>
+    <x:t>episode_affinity_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_01의 호감도 30 달성 시 해금</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호감도 테스트 에피소드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EpisodeDescription</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsArchiveVisible</x:t>
+  </x:si>
   <x:si>
     <x:t>4일차에 발생하는 테스트 에피소드</x:t>
   </x:si>
   <x:si>
-    <x:t>5일차에 발생하는 테스트 에피소드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsArchiveVisible</x:t>
+    <x:t>3일차에 발생하는 테스트 에피소드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>재생 방식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에피소드 분류</x:t>
   </x:si>
   <x:si>
     <x:t>Archive</x:t>
   </x:si>
   <x:si>
-    <x:t>에피소드 분류</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
+    <x:t>에피소드 내용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에피소드 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에피소드ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Auto</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반복 발생 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DialogueId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>테스트 에피소드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연결 다이얼로그 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EpisodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최대 발생 횟수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도감 노출 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Category</x:t>
+  </x:si>
+  <x:si>
+    <x:t>episode_test_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxTriggerCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>episode_test_01</x:t>
   </x:si>
   <x:si>
     <x:t>PlaybackType</x:t>
   </x:si>
   <x:si>
     <x:t>IsRepeatable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxTriggerCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>episode_test_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>재생 방식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에피소드 내용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에피소드ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에피소드 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DialogueId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EpisodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>테스트 에피소드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연결 다이얼로그 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반복 발생 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최대 발생 횟수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>episode_test_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EpisodeDescription</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3일차에 발생하는 테스트 에피소드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도감 노출 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Main</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Daily</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Category</x:t>
-  </x:si>
-  <x:si>
-    <x:t>episode_test_02</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -259,7 +250,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="18">
+  <x:cellXfs count="19">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -344,6 +335,9 @@
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -952,7 +946,7 @@
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="19.42578125" style="3" customWidth="1"/>
-    <x:col min="2" max="2" width="19.5703125" style="3" customWidth="1"/>
+    <x:col min="2" max="2" width="22.859375" style="3" bestFit="1" customWidth="1"/>
     <x:col min="3" max="3" width="32.76171875" style="3" bestFit="1" customWidth="1"/>
     <x:col min="4" max="7" width="20.28515625" style="3" customWidth="1"/>
     <x:col min="8" max="8" width="30.5703125" style="3" customWidth="1"/>
@@ -962,51 +956,51 @@
   <x:sheetData>
     <x:row r="1" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="s">
         <x:v>15</x:v>
-      </x:c>
-      <x:c r="B1" s="1" t="s">
-        <x:v>16</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D1" s="13" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E1" s="13" t="s">
-        <x:v>4</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F1" s="13" t="s">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G1" s="13" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="I1" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:9" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>14</x:v>
@@ -1015,56 +1009,56 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9" s="11" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="14" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B3" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C3" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B3" s="14" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C3" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="D3" s="14" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E3" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F3" s="14" t="s">
-        <x:v>7</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G3" s="14" t="s">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H3" s="14" t="s">
-        <x:v>8</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="I3" s="15" t="s">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A4" s="16" t="s">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B4" s="16" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C4" s="16" t="s">
-        <x:v>29</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D4" s="16" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="E4" s="16" t="s">
-        <x:v>33</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F4" s="16" t="s">
-        <x:v>3</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G4" s="16" t="b">
         <x:v>1</x:v>
@@ -1085,22 +1079,22 @@
     </x:row>
     <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A5" s="16" t="s">
-        <x:v>35</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B5" s="16" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C5" s="16" t="s">
-        <x:v>0</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D5" s="16" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E5" s="16" t="s">
-        <x:v>31</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E5" s="18" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F5" s="16" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G5" s="16" t="b">
         <x:v>1</x:v>
@@ -1120,32 +1114,32 @@
       <x:c r="P5" s="5"/>
     </x:row>
     <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
-      <x:c r="A6" s="16" t="s">
-        <x:v>24</x:v>
+      <x:c r="A6" s="18" t="s">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B6" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C6" s="16" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C6" s="18" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D6" s="16" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E6" s="18" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="E6" s="16" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F6" s="16" t="s">
-        <x:v>27</x:v>
+      <x:c r="F6" s="18" t="s">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G6" s="16" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H6" s="16" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H6" s="16" t="b">
+      <x:c r="I6" s="17">
         <x:v>1</x:v>
-      </x:c>
-      <x:c r="I6" s="17">
-        <x:v>3</x:v>
       </x:c>
       <x:c r="J6" s="5"/>
       <x:c r="K6" s="5"/>

--- a/JsonConverter/ExcelFiles/Episode.xlsx
+++ b/JsonConverter/ExcelFiles/Episode.xlsx
@@ -19,105 +19,114 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="36">
   <x:si>
     <x:t>episode_affinity_01</x:t>
   </x:si>
   <x:si>
+    <x:t>IsArchiveVisible</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EpisodeDescription</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3일차에 발생하는 테스트 에피소드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4일차에 발생하는 테스트 에피소드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시설 건설 테스트 에피소드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archive</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에피소드 내용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에피소드 분류</x:t>
+  </x:si>
+  <x:si>
+    <x:t>재생 방식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에피소드 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Auto</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에피소드ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>특정 시설을 건설하면 해금되는 테스트 에피소드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsRepeatable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호감도 테스트 에피소드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>episode_test_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxTriggerCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>episode_test_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PlaybackType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반복 발생 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DialogueId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연결 다이얼로그 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도감 노출 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Category</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EpisodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최대 발생 횟수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>테스트 에피소드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character</x:t>
+  </x:si>
+  <x:si>
     <x:t>hero_01의 호감도 30 달성 시 해금</x:t>
   </x:si>
   <x:si>
-    <x:t>호감도 테스트 에피소드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EpisodeDescription</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsArchiveVisible</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4일차에 발생하는 테스트 에피소드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3일차에 발생하는 테스트 에피소드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>재생 방식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에피소드 분류</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archive</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에피소드 내용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에피소드 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에피소드ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반복 발생 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DialogueId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>테스트 에피소드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연결 다이얼로그 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EpisodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최대 발생 횟수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도감 노출 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Category</x:t>
-  </x:si>
-  <x:si>
-    <x:t>episode_test_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxTriggerCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>episode_test_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PlaybackType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsRepeatable</x:t>
+    <x:t>episode_room_01</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -160,22 +169,53 @@
       <x:sz val="10"/>
       <x:color rgb="ff000000"/>
     </x:font>
-    <x:font>
-      <x:name val="맑은 고딕"/>
-      <x:sz val="10"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="맑은 고딕"/>
+          <x:sz val="10"/>
+          <x:color rgb="ff000000"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="맑은 고딕"/>
+          <x:sz val="10"/>
+          <x:color rgb="ff000000"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
     <x:font>
       <x:name val="맑은 고딕"/>
       <x:sz val="11"/>
       <x:color rgb="ff000000"/>
     </x:font>
-    <x:font>
-      <x:name val="맑은 고딕"/>
-      <x:sz val="11"/>
-      <x:color rgb="ff000000"/>
-      <x:b val="1"/>
-    </x:font>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="맑은 고딕"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff000000"/>
+          <x:b val="1"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="맑은 고딕"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff000000"/>
+          <x:b val="1"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
   </x:fonts>
   <x:fills count="7">
     <x:fill>
@@ -946,8 +986,8 @@
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="19.42578125" style="3" customWidth="1"/>
-    <x:col min="2" max="2" width="22.859375" style="3" bestFit="1" customWidth="1"/>
-    <x:col min="3" max="3" width="32.76171875" style="3" bestFit="1" customWidth="1"/>
+    <x:col min="2" max="2" width="25.55859375" style="3" bestFit="1" customWidth="1"/>
+    <x:col min="3" max="3" width="45" style="3" bestFit="1" customWidth="1"/>
     <x:col min="4" max="7" width="20.28515625" style="3" customWidth="1"/>
     <x:col min="8" max="8" width="30.5703125" style="3" customWidth="1"/>
     <x:col min="9" max="9" width="26.5703125" style="3" customWidth="1"/>
@@ -956,109 +996,109 @@
   <x:sheetData>
     <x:row r="1" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D1" s="13" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E1" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F1" s="13" t="s">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G1" s="13" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="I1" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:9" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9" s="11" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="14" t="s">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B3" s="14" t="s">
-        <x:v>22</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3" s="14" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D3" s="14" t="s">
-        <x:v>19</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E3" s="14" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F3" s="14" t="s">
-        <x:v>31</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G3" s="14" t="s">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H3" s="14" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="I3" s="15" t="s">
-        <x:v>29</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A4" s="16" t="s">
-        <x:v>30</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B4" s="16" t="s">
-        <x:v>20</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C4" s="16" t="s">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D4" s="16" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E4" s="16" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F4" s="16" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G4" s="16" t="b">
         <x:v>1</x:v>
@@ -1079,22 +1119,22 @@
     </x:row>
     <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A5" s="16" t="s">
-        <x:v>28</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B5" s="16" t="s">
-        <x:v>20</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C5" s="16" t="s">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D5" s="16" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E5" s="18" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F5" s="16" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G5" s="16" t="b">
         <x:v>1</x:v>
@@ -1118,19 +1158,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B6" s="16" t="s">
-        <x:v>2</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="18" t="s">
-        <x:v>1</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D6" s="16" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E6" s="18" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F6" s="18" t="s">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G6" s="16" t="b">
         <x:v>1</x:v>
@@ -1150,15 +1190,33 @@
       <x:c r="P6" s="5"/>
     </x:row>
     <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
-      <x:c r="A7" s="4"/>
-      <x:c r="B7" s="4"/>
-      <x:c r="C7" s="4"/>
-      <x:c r="D7" s="12"/>
-      <x:c r="E7" s="12"/>
-      <x:c r="F7" s="12"/>
-      <x:c r="G7" s="12"/>
-      <x:c r="H7" s="12"/>
-      <x:c r="I7" s="12"/>
+      <x:c r="A7" s="18" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B7" s="16" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C7" s="18" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D7" s="16" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E7" s="18" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F7" s="18" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G7" s="16" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H7" s="16" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I7" s="17">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="J7" s="5"/>
       <x:c r="K7" s="5"/>
       <x:c r="L7" s="5"/>

--- a/JsonConverter/ExcelFiles/Episode.xlsx
+++ b/JsonConverter/ExcelFiles/Episode.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="17868" windowHeight="6312"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="22788" windowHeight="8520"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="HeroBasic" sheetId="1" r:id="rId4"/>
@@ -19,7 +19,76 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="36">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="39">
+  <x:si>
+    <x:t>episode_admitted_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Category</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반복 발생 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EpisodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최대 발생 횟수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DialogueId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연결 다이얼로그 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>테스트 에피소드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도감 노출 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>재생 방식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archive</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에피소드ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에피소드 내용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Auto</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에피소드 분류</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에피소드 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4일차에 발생하는 테스트 에피소드</x:t>
+  </x:si>
   <x:si>
     <x:t>episode_affinity_01</x:t>
   </x:si>
@@ -27,106 +96,46 @@
     <x:t>IsArchiveVisible</x:t>
   </x:si>
   <x:si>
+    <x:t>3일차에 발생하는 테스트 에피소드</x:t>
+  </x:si>
+  <x:si>
     <x:t>EpisodeDescription</x:t>
   </x:si>
   <x:si>
-    <x:t>3일차에 발생하는 테스트 에피소드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4일차에 발생하는 테스트 에피소드</x:t>
+    <x:t>특정 시설을 건설하면 해금되는 테스트 에피소드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_01의 호감도 30 달성 시 해금</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PlaybackType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호감도 테스트 에피소드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>episode_room_01</x:t>
   </x:si>
   <x:si>
     <x:t>시설 건설 테스트 에피소드</x:t>
   </x:si>
   <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archive</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에피소드 내용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에피소드 분류</x:t>
-  </x:si>
-  <x:si>
-    <x:t>재생 방식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에피소드 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에피소드ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>특정 시설을 건설하면 해금되는 테스트 에피소드</x:t>
+    <x:t>MaxTriggerCount</x:t>
   </x:si>
   <x:si>
     <x:t>IsRepeatable</x:t>
   </x:si>
   <x:si>
-    <x:t>호감도 테스트 에피소드</x:t>
+    <x:t>episode_test_01</x:t>
   </x:si>
   <x:si>
     <x:t>episode_test_02</x:t>
   </x:si>
   <x:si>
-    <x:t>MaxTriggerCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>episode_test_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PlaybackType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반복 발생 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DialogueId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연결 다이얼로그 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도감 노출 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Category</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EpisodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최대 발생 횟수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>테스트 에피소드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_01의 호감도 30 달성 시 해금</x:t>
-  </x:si>
-  <x:si>
-    <x:t>episode_room_01</x:t>
+    <x:t>특정 영웅이 입소해 있으면 해금되는 테스트 에피소드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>입소 테스트 에피소드</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -169,53 +178,22 @@
       <x:sz val="10"/>
       <x:color rgb="ff000000"/>
     </x:font>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="맑은 고딕"/>
-          <x:sz val="10"/>
-          <x:color rgb="ff000000"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="맑은 고딕"/>
-          <x:sz val="10"/>
-          <x:color rgb="ff000000"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
+    <x:font>
+      <x:name val="맑은 고딕"/>
+      <x:sz val="10"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
     <x:font>
       <x:name val="맑은 고딕"/>
       <x:sz val="11"/>
       <x:color rgb="ff000000"/>
     </x:font>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="맑은 고딕"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-          <x:b val="1"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="맑은 고딕"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-          <x:b val="1"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
+    <x:font>
+      <x:name val="맑은 고딕"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+      <x:b val="1"/>
+    </x:font>
   </x:fonts>
   <x:fills count="7">
     <x:fill>
@@ -996,109 +974,109 @@
   <x:sheetData>
     <x:row r="1" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D1" s="13" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E1" s="13" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F1" s="13" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G1" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D1" s="13" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E1" s="13" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F1" s="13" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G1" s="13" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I1" s="3" t="s">
-        <x:v>31</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:9" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9" s="11" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="14" t="s">
-        <x:v>6</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B3" s="14" t="s">
-        <x:v>30</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C3" s="14" t="s">
-        <x:v>2</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D3" s="14" t="s">
-        <x:v>25</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E3" s="14" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F3" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="F3" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="G3" s="14" t="s">
-        <x:v>1</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H3" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="I3" s="15" t="s">
-        <x:v>21</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A4" s="16" t="s">
-        <x:v>22</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B4" s="16" t="s">
-        <x:v>32</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C4" s="16" t="s">
-        <x:v>3</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D4" s="16" t="s">
-        <x:v>27</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E4" s="16" t="s">
-        <x:v>33</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F4" s="16" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G4" s="16" t="b">
         <x:v>1</x:v>
@@ -1119,22 +1097,22 @@
     </x:row>
     <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A5" s="16" t="s">
-        <x:v>20</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B5" s="16" t="s">
-        <x:v>32</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C5" s="16" t="s">
-        <x:v>4</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D5" s="16" t="s">
-        <x:v>27</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E5" s="18" t="s">
-        <x:v>33</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F5" s="16" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G5" s="16" t="b">
         <x:v>1</x:v>
@@ -1155,22 +1133,22 @@
     </x:row>
     <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A6" s="18" t="s">
-        <x:v>0</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B6" s="16" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C6" s="18" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D6" s="16" t="s">
-        <x:v>27</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E6" s="18" t="s">
-        <x:v>33</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F6" s="18" t="s">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G6" s="16" t="b">
         <x:v>1</x:v>
@@ -1191,22 +1169,22 @@
     </x:row>
     <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A7" s="18" t="s">
-        <x:v>35</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B7" s="16" t="s">
-        <x:v>5</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C7" s="18" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D7" s="16" t="s">
-        <x:v>27</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E7" s="18" t="s">
-        <x:v>33</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F7" s="18" t="s">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G7" s="16" t="b">
         <x:v>1</x:v>
@@ -1226,15 +1204,33 @@
       <x:c r="P7" s="5"/>
     </x:row>
     <x:row r="8" spans="1:16" ht="15.75" customHeight="1">
-      <x:c r="A8" s="4"/>
-      <x:c r="B8" s="6"/>
-      <x:c r="C8" s="6"/>
-      <x:c r="D8" s="12"/>
-      <x:c r="E8" s="12"/>
-      <x:c r="F8" s="12"/>
-      <x:c r="G8" s="12"/>
-      <x:c r="H8" s="12"/>
-      <x:c r="I8" s="12"/>
+      <x:c r="A8" s="4" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D8" s="12" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E8" s="12" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F8" s="12" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G8" s="12" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H8" s="12" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="J8" s="5"/>
       <x:c r="K8" s="5"/>
       <x:c r="L8" s="5"/>
